--- a/Outputs/0. Current Case/Output_0_40.xlsx
+++ b/Outputs/0. Current Case/Output_0_40.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailaub-my.sharepoint.com/personal/mo10_aub_edu_lb/Documents/3-Research/Elsa/Model 1/Github/microgrid_MP/Outputs/0. Current Case/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_82D144728668A56124BCB81F8C823694C392EB68" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12ECD03A-7586-4E0F-BAF9-40C6BB7839EA}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_82D144728668A56124BCB81F8C823694C392EB68" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{716B948F-717B-4EF1-BF8D-6BAB6ACA42E1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,8 +31,11 @@
     <sheet name="Unmet Demand" sheetId="16" r:id="rId16"/>
     <sheet name="Household Surplus" sheetId="17" r:id="rId17"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -628,6 +631,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="29.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B1" s="1">
@@ -25702,6 +25708,7 @@
   <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
